--- a/result/6组对比实验.xlsx
+++ b/result/6组对比实验.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="21600" windowHeight="9555"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="15">
   <si>
     <t>高频</t>
   </si>
@@ -247,12 +247,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -573,7 +585,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
@@ -597,16 +609,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
@@ -615,89 +627,89 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -707,7 +719,25 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1024,19 +1054,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="6"/>
+  <dimension ref="A1:L8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="10.875" customWidth="1"/>
+    <col min="1" max="1" width="10.8761061946903" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="13.75" customWidth="1"/>
-    <col min="4" max="4" width="13.5" customWidth="1"/>
-    <col min="5" max="5" width="12.25" customWidth="1"/>
-    <col min="6" max="6" width="14.375" customWidth="1"/>
-    <col min="7" max="7" width="11.875" customWidth="1"/>
+    <col min="3" max="3" width="13.7522123893805" customWidth="1"/>
+    <col min="4" max="5" width="13.5044247787611" customWidth="1"/>
+    <col min="6" max="6" width="12.2477876106195" customWidth="1"/>
+    <col min="7" max="7" width="14.3716814159292" customWidth="1"/>
+    <col min="8" max="9" width="11.8761061946903" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.75" spans="1:7">
+    <row r="1" ht="17.6" spans="1:12">
       <c r="A1" s="1"/>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -1047,17 +1077,28 @@
       <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="2"/>
+      <c r="F1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="I1" s="2"/>
+      <c r="J1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" ht="18.75" spans="1:7">
+    <row r="2" ht="17.6" spans="1:12">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -1070,18 +1111,29 @@
       <c r="D2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="1"/>
+      <c r="F2" s="5">
         <v>0.005</v>
       </c>
-      <c r="F2" s="1">
+      <c r="G2" s="5">
         <v>0.9969</v>
       </c>
-      <c r="G2" s="3">
+      <c r="H2" s="6">
         <v>0.0047</v>
       </c>
+      <c r="I2" s="7"/>
+      <c r="J2" s="8">
+        <v>0.0041</v>
+      </c>
+      <c r="K2" s="8">
+        <v>0.9979</v>
+      </c>
+      <c r="L2" s="9">
+        <v>0.0034</v>
+      </c>
     </row>
-    <row r="3" ht="18.75" spans="1:7">
-      <c r="A3" s="4" t="s">
+    <row r="3" ht="17.6" spans="1:12">
+      <c r="A3" s="10" t="s">
         <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -1093,18 +1145,29 @@
       <c r="D3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" s="1"/>
+      <c r="F3" s="5">
         <v>0.004</v>
       </c>
-      <c r="F3" s="1">
+      <c r="G3" s="5">
         <v>0.998</v>
       </c>
-      <c r="G3" s="3">
+      <c r="H3" s="6">
         <v>0.0031</v>
       </c>
+      <c r="I3" s="7"/>
+      <c r="J3" s="8">
+        <v>0.0049</v>
+      </c>
+      <c r="K3" s="8">
+        <v>0.997</v>
+      </c>
+      <c r="L3" s="9">
+        <v>0.0045</v>
+      </c>
     </row>
-    <row r="4" ht="18.75" spans="1:7">
-      <c r="A4" s="4" t="s">
+    <row r="4" ht="17.6" spans="1:12">
+      <c r="A4" s="10" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -1116,18 +1179,29 @@
       <c r="D4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" s="1"/>
+      <c r="F4" s="5">
         <v>0.0043</v>
       </c>
-      <c r="F4" s="1">
+      <c r="G4" s="5">
         <v>0.9977</v>
       </c>
-      <c r="G4" s="3">
+      <c r="H4" s="6">
         <v>0.0037</v>
       </c>
+      <c r="I4" s="7"/>
+      <c r="J4" s="8">
+        <v>0.0049</v>
+      </c>
+      <c r="K4" s="8">
+        <v>0.9971</v>
+      </c>
+      <c r="L4" s="9">
+        <v>0.0043</v>
+      </c>
     </row>
-    <row r="5" ht="18.75" spans="1:7">
-      <c r="A5" s="4" t="s">
+    <row r="5" ht="17.6" spans="1:12">
+      <c r="A5" s="10" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -1139,17 +1213,28 @@
       <c r="D5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5" s="1"/>
+      <c r="F5" s="5">
         <v>0.0044</v>
       </c>
-      <c r="F5" s="1">
+      <c r="G5" s="5">
         <v>0.9976</v>
       </c>
-      <c r="G5" s="3">
+      <c r="H5" s="6">
         <v>0.0037</v>
       </c>
+      <c r="I5" s="7"/>
+      <c r="J5" s="8">
+        <v>0.0047</v>
+      </c>
+      <c r="K5" s="8">
+        <v>0.9973</v>
+      </c>
+      <c r="L5" s="9">
+        <v>0.0042</v>
+      </c>
     </row>
-    <row r="6" ht="18.75" spans="1:7">
+    <row r="6" ht="17.6" spans="1:12">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
@@ -1162,17 +1247,28 @@
       <c r="D6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" s="1"/>
+      <c r="F6" s="5">
         <v>0.0041</v>
       </c>
-      <c r="F6" s="1">
+      <c r="G6" s="5">
         <v>0.9979</v>
       </c>
-      <c r="G6" s="3">
+      <c r="H6" s="6">
         <v>0.0034</v>
       </c>
+      <c r="I6" s="7"/>
+      <c r="J6" s="8">
+        <v>0.0045</v>
+      </c>
+      <c r="K6" s="8">
+        <v>0.9975</v>
+      </c>
+      <c r="L6" s="9">
+        <v>0.004</v>
+      </c>
     </row>
-    <row r="7" ht="18.75" spans="1:7">
+    <row r="7" ht="17.6" spans="1:12">
       <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
@@ -1185,17 +1281,28 @@
       <c r="D7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" s="1"/>
+      <c r="F7" s="5">
         <v>0.0043</v>
       </c>
-      <c r="F7" s="1">
+      <c r="G7" s="5">
         <v>0.9977</v>
       </c>
-      <c r="G7" s="3">
+      <c r="H7" s="6">
         <v>0.0038</v>
       </c>
+      <c r="I7" s="7"/>
+      <c r="J7" s="8">
+        <v>0.004</v>
+      </c>
+      <c r="K7" s="8">
+        <v>0.998</v>
+      </c>
+      <c r="L7" s="9">
+        <v>0.0032</v>
+      </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:12">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -1203,6 +1310,8 @@
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
